--- a/nr-add-cip/ig/ValueSet-fr-substance-code.xlsx
+++ b/nr-add-cip/ig/ValueSet-fr-substance-code.xlsx
@@ -9,12 +9,14 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Include #0" r:id="rId4" sheetId="2"/>
     <sheet name="Include #1" r:id="rId5" sheetId="3"/>
+    <sheet name="Include #2" r:id="rId6" sheetId="4"/>
+    <sheet name="Include #3" r:id="rId7" sheetId="5"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="37">
   <si>
     <t>Property</t>
   </si>
@@ -61,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-02T15:38:39+00:00</t>
+    <t>2026-02-02T15:38:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -119,6 +121,12 @@
   </si>
   <si>
     <t>http://data.esante.gouv.fr/ansm/medicament/substance</t>
+  </si>
+  <si>
+    <t>http://data.esante.gouv.fr/ansm/medicament/UCD</t>
+  </si>
+  <si>
+    <t>http://data.esante.gouv.fr/ansm/medicament/SpecialitePharmaceutique</t>
   </si>
 </sst>
 </file>
@@ -466,4 +474,84 @@
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>35</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>36</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
 </file>
--- a/nr-add-cip/ig/ValueSet-fr-substance-code.xlsx
+++ b/nr-add-cip/ig/ValueSet-fr-substance-code.xlsx
@@ -9,14 +9,12 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Include #0" r:id="rId4" sheetId="2"/>
     <sheet name="Include #1" r:id="rId5" sheetId="3"/>
-    <sheet name="Include #2" r:id="rId6" sheetId="4"/>
-    <sheet name="Include #3" r:id="rId7" sheetId="5"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="35">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-02T15:38:16+00:00</t>
+    <t>2026-02-23T08:39:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -121,12 +119,6 @@
   </si>
   <si>
     <t>http://data.esante.gouv.fr/ansm/medicament/substance</t>
-  </si>
-  <si>
-    <t>http://data.esante.gouv.fr/ansm/medicament/UCD</t>
-  </si>
-  <si>
-    <t>http://data.esante.gouv.fr/ansm/medicament/SpecialitePharmaceutique</t>
   </si>
 </sst>
 </file>
@@ -474,84 +466,4 @@
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <cols>
-    <col min="1" max="1" width="30.703125" customWidth="true"/>
-    <col min="2" max="2" width="50.703125" customWidth="true"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="1">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>35</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <cols>
-    <col min="1" max="1" width="30.703125" customWidth="true"/>
-    <col min="2" max="2" width="50.703125" customWidth="true"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="1">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>36</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
 </file>